--- a/data/trans_orig/P36B06_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Edad-trans_orig.xlsx
@@ -537,7 +537,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2007 (tasa de respuesta: 99,92%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>299430</t>
+          <t>301942</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>342480</t>
+          <t>343043</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>60,73%</t>
+          <t>61,24%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,47%</t>
+          <t>69,58%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>290556</t>
+          <t>293125</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>330067</t>
+          <t>331978</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,29%</t>
+          <t>62,84%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,76%</t>
+          <t>71,17%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>605783</t>
+          <t>604272</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>662705</t>
+          <t>662621</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>63,14%</t>
+          <t>62,98%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,07%</t>
+          <t>69,06%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>150542</t>
+          <t>149979</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>193592</t>
+          <t>191080</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,53%</t>
+          <t>30,42%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>39,27%</t>
+          <t>38,76%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>136362</t>
+          <t>134451</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>175873</t>
+          <t>173304</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,24%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,71%</t>
+          <t>37,16%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>296746</t>
+          <t>296830</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>353668</t>
+          <t>355179</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,93%</t>
+          <t>30,94%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>36,86%</t>
+          <t>37,02%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>503690</t>
+          <t>506754</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>553647</t>
+          <t>554642</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,57%</t>
+          <t>68,99%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,37%</t>
+          <t>75,51%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>470401</t>
+          <t>467360</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>510895</t>
+          <t>507817</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>74,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,68%</t>
+          <t>81,19%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>989841</t>
+          <t>983873</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1055453</t>
+          <t>1050528</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,78%</t>
+          <t>72,34%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,6%</t>
+          <t>77,24%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>180894</t>
+          <t>179899</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>230851</t>
+          <t>227787</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,63%</t>
+          <t>24,49%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,43%</t>
+          <t>31,01%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>114599</t>
+          <t>117677</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>155093</t>
+          <t>158134</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,32%</t>
+          <t>18,81%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>25,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>304581</t>
+          <t>309506</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>370193</t>
+          <t>376161</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,4%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,22%</t>
+          <t>27,66%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>470327</t>
+          <t>471440</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>515161</t>
+          <t>513880</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,74%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>80,57%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>547373</t>
+          <t>547388</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>588080</t>
+          <t>587870</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1473,7 +1473,7 @@
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,26%</t>
+          <t>85,23%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1031712</t>
+          <t>1029371</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1089181</t>
+          <t>1089515</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,72%</t>
+          <t>77,54%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,05%</t>
+          <t>82,07%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>122625</t>
+          <t>123906</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>167459</t>
+          <t>166346</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>19,43%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,26%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101664</t>
+          <t>101874</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142371</t>
+          <t>142356</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,7 +1581,7 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,74%</t>
+          <t>14,77%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238349</t>
+          <t>238015</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>295818</t>
+          <t>298159</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,95%</t>
+          <t>17,93%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,28%</t>
+          <t>22,46%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>390277</t>
+          <t>389779</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>429262</t>
+          <t>426312</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1776,12 +1776,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>75,18%</t>
+          <t>75,08%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,69%</t>
+          <t>82,12%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>423119</t>
+          <t>421925</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>456057</t>
+          <t>454403</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>81,98%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,61%</t>
+          <t>88,29%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>822330</t>
+          <t>825522</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>871532</t>
+          <t>874018</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,54%</t>
+          <t>79,85%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,3%</t>
+          <t>84,54%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>89885</t>
+          <t>92835</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>128870</t>
+          <t>129368</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,12 +1889,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,31%</t>
+          <t>17,88%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>24,82%</t>
+          <t>24,92%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>58609</t>
+          <t>60263</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>91547</t>
+          <t>92741</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,39%</t>
+          <t>11,71%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>18,02%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>162281</t>
+          <t>159795</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>211483</t>
+          <t>208291</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,7%</t>
+          <t>15,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,46%</t>
+          <t>20,15%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>298156</t>
+          <t>298941</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328715</t>
+          <t>328904</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,1%</t>
+          <t>77,3%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,0%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>337168</t>
+          <t>335054</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>364002</t>
+          <t>363754</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,46%</t>
+          <t>82,94%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,1%</t>
+          <t>90,04%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>642992</t>
+          <t>644059</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>684503</t>
+          <t>685590</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,32%</t>
+          <t>81,45%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,57%</t>
+          <t>86,71%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57995</t>
+          <t>57806</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>88554</t>
+          <t>87769</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>15,0%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,9%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>39984</t>
+          <t>40232</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>66818</t>
+          <t>68932</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,9%</t>
+          <t>9,96%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,54%</t>
+          <t>17,06%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>106193</t>
+          <t>105106</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>147704</t>
+          <t>146637</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,43%</t>
+          <t>13,29%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,68%</t>
+          <t>18,55%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>236341</t>
+          <t>235281</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>260327</t>
+          <t>258863</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,78%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,98%</t>
+          <t>88,48%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>294074</t>
+          <t>292413</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>316072</t>
+          <t>315044</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,75%</t>
+          <t>85,27%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>92,17%</t>
+          <t>91,87%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>536546</t>
+          <t>535068</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>569622</t>
+          <t>569473</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,43%</t>
+          <t>84,19%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,63%</t>
+          <t>89,61%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>32256</t>
+          <t>33720</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>56242</t>
+          <t>57302</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,02%</t>
+          <t>11,52%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,22%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>26862</t>
+          <t>27890</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>48860</t>
+          <t>50521</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>7,83%</t>
+          <t>8,13%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,25%</t>
+          <t>14,73%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>65895</t>
+          <t>66044</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>98971</t>
+          <t>100449</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,37%</t>
+          <t>10,39%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,57%</t>
+          <t>15,81%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>167632</t>
+          <t>165516</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187479</t>
+          <t>187327</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>79,87%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,25%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>274339</t>
+          <t>276406</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301455</t>
+          <t>301469</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,16%</t>
+          <t>82,78%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,28%</t>
+          <t>90,29%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>448250</t>
+          <t>449438</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>481624</t>
+          <t>483048</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,43%</t>
+          <t>82,65%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,57%</t>
+          <t>88,83%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22404</t>
+          <t>22556</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>42251</t>
+          <t>44367</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>20,13%</t>
+          <t>21,14%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32453</t>
+          <t>32439</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>59569</t>
+          <t>57502</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,72%</t>
+          <t>9,71%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,84%</t>
+          <t>17,22%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>62167</t>
+          <t>60743</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>95541</t>
+          <t>94353</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,43%</t>
+          <t>11,17%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,57%</t>
+          <t>17,35%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2449382</t>
+          <t>2451498</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2544630</t>
+          <t>2550722</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,82%</t>
+          <t>74,89%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,73%</t>
+          <t>77,92%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2709677</t>
+          <t>2713392</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2799375</t>
+          <t>2798214</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,24%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,89%</t>
+          <t>82,86%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5177785</t>
+          <t>5185270</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5322608</t>
+          <t>5322071</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,85%</t>
+          <t>77,96%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,03%</t>
+          <t>80,02%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>729041</t>
+          <t>722949</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>824289</t>
+          <t>822173</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,27%</t>
+          <t>22,08%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,18%</t>
+          <t>25,11%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>577787</t>
+          <t>578948</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>667485</t>
+          <t>663770</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,11%</t>
+          <t>17,14%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,76%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1328225</t>
+          <t>1328762</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1473048</t>
+          <t>1465563</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,97%</t>
+          <t>19,98%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,15%</t>
+          <t>22,04%</t>
         </is>
       </c>
     </row>
@@ -3516,7 +3516,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2012 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>312064</t>
+          <t>312955</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>350174</t>
+          <t>351381</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,71%</t>
+          <t>68,91%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,11%</t>
+          <t>77,37%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>314980</t>
+          <t>313549</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>349399</t>
+          <t>348436</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>73,21%</t>
+          <t>72,88%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>81,21%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>637468</t>
+          <t>636471</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>688559</t>
+          <t>689055</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>72,08%</t>
+          <t>71,97%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,86%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>103972</t>
+          <t>102765</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>142082</t>
+          <t>141191</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,89%</t>
+          <t>22,63%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,29%</t>
+          <t>31,09%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>80831</t>
+          <t>81794</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>115250</t>
+          <t>116681</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>18,79%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>26,79%</t>
+          <t>27,12%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195817</t>
+          <t>195321</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>246908</t>
+          <t>247905</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,14%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>27,92%</t>
+          <t>28,03%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>501436</t>
+          <t>501516</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>545321</t>
+          <t>546181</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,08%</t>
+          <t>73,09%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,48%</t>
+          <t>79,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>498771</t>
+          <t>498469</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>534399</t>
+          <t>534702</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,86%</t>
+          <t>81,81%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,71%</t>
+          <t>87,76%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1011458</t>
+          <t>1011924</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1073559</t>
+          <t>1069443</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,08%</t>
+          <t>78,12%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,87%</t>
+          <t>82,56%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>140807</t>
+          <t>139947</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184692</t>
+          <t>184612</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,52%</t>
+          <t>20,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,92%</t>
+          <t>26,91%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74870</t>
+          <t>74567</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110498</t>
+          <t>110800</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,29%</t>
+          <t>12,24%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,14%</t>
+          <t>18,19%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>221839</t>
+          <t>225955</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>283940</t>
+          <t>283474</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,13%</t>
+          <t>17,44%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,92%</t>
+          <t>21,88%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>542154</t>
+          <t>541813</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>580582</t>
+          <t>580555</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,51%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,15%</t>
+          <t>85,14%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>598385</t>
+          <t>600332</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>633983</t>
+          <t>634855</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,32%</t>
+          <t>84,59%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,46%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1152868</t>
+          <t>1150923</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1207769</t>
+          <t>1205305</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,85%</t>
+          <t>82,71%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,79%</t>
+          <t>86,62%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101281</t>
+          <t>101308</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>139709</t>
+          <t>140050</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,85%</t>
+          <t>14,86%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,49%</t>
+          <t>20,54%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>75689</t>
+          <t>74817</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>111287</t>
+          <t>109340</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,54%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,68%</t>
+          <t>15,41%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183765</t>
+          <t>186229</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>238666</t>
+          <t>240611</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,21%</t>
+          <t>13,38%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,15%</t>
+          <t>17,29%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>511995</t>
+          <t>513360</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>548059</t>
+          <t>547537</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,58%</t>
+          <t>83,81%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,47%</t>
+          <t>89,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>539351</t>
+          <t>540760</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>572163</t>
+          <t>571607</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,68%</t>
+          <t>87,91%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,92%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1062381</t>
+          <t>1064517</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1111188</t>
+          <t>1112607</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,53%</t>
+          <t>86,71%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,51%</t>
+          <t>90,63%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>64505</t>
+          <t>65027</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>100569</t>
+          <t>99204</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,53%</t>
+          <t>10,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,42%</t>
+          <t>16,19%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>42975</t>
+          <t>43531</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>75787</t>
+          <t>74378</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,08%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,32%</t>
+          <t>12,09%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>116515</t>
+          <t>115096</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>165322</t>
+          <t>163186</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,49%</t>
+          <t>9,37%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,47%</t>
+          <t>13,29%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>371902</t>
+          <t>371344</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>397110</t>
+          <t>397513</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5098,12 +5098,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>86,6%</t>
+          <t>86,47%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,47%</t>
+          <t>92,57%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>375821</t>
+          <t>376266</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>406805</t>
+          <t>406298</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>83,93%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,85%</t>
+          <t>90,73%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>753199</t>
+          <t>756984</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>794139</t>
+          <t>795800</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>85,86%</t>
+          <t>86,29%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,53%</t>
+          <t>90,72%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>32319</t>
+          <t>31916</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>57527</t>
+          <t>58085</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,12 +5211,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,53%</t>
+          <t>7,43%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>13,4%</t>
+          <t>13,53%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>41502</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71979</t>
+          <t>71534</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,15%</t>
+          <t>9,27%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>16,07%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>83090</t>
+          <t>81429</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>124030</t>
+          <t>120245</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,47%</t>
+          <t>9,28%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>14,14%</t>
+          <t>13,71%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>270213</t>
+          <t>269312</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>290183</t>
+          <t>290350</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,21%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>93,97%</t>
+          <t>94,02%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>322903</t>
+          <t>323536</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>340478</t>
+          <t>341152</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,22%</t>
+          <t>91,4%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,18%</t>
+          <t>96,37%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>600145</t>
+          <t>600255</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>627880</t>
+          <t>627121</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>90,55%</t>
+          <t>90,56%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,73%</t>
+          <t>94,62%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18621</t>
+          <t>18454</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>38591</t>
+          <t>39492</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>6,03%</t>
+          <t>5,98%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,79%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>13518</t>
+          <t>12844</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>31093</t>
+          <t>30460</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,82%</t>
+          <t>3,63%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,78%</t>
+          <t>8,6%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>34920</t>
+          <t>35679</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62655</t>
+          <t>62545</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,27%</t>
+          <t>5,38%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,45%</t>
+          <t>9,44%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227248</t>
+          <t>227632</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243391</t>
+          <t>243268</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,34%</t>
+          <t>91,5%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,83%</t>
+          <t>97,78%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>355084</t>
+          <t>353797</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>373027</t>
+          <t>372770</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>92,26%</t>
+          <t>91,93%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,92%</t>
+          <t>96,86%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>588358</t>
+          <t>589359</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>612969</t>
+          <t>612722</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>92,85%</t>
+          <t>93,01%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,74%</t>
+          <t>96,7%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5391</t>
+          <t>5514</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21534</t>
+          <t>21150</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,17%</t>
+          <t>2,22%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,66%</t>
+          <t>8,5%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>11840</t>
+          <t>12097</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>29783</t>
+          <t>31070</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,08%</t>
+          <t>3,14%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>7,74%</t>
+          <t>8,07%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20680</t>
+          <t>20927</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>45291</t>
+          <t>44290</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,26%</t>
+          <t>3,3%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>7,15%</t>
+          <t>6,99%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2812667</t>
+          <t>2801621</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2899943</t>
+          <t>2893006</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>82,2%</t>
+          <t>81,88%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,75%</t>
+          <t>84,55%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3078892</t>
+          <t>3070752</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3154466</t>
+          <t>3152914</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,48%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,79%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5912374</t>
+          <t>5907117</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6029929</t>
+          <t>6026951</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,79%</t>
+          <t>84,72%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,44%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>521774</t>
+          <t>528711</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>609050</t>
+          <t>620096</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,25%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>17,8%</t>
+          <t>18,12%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>396506</t>
+          <t>398058</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>472080</t>
+          <t>480220</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,21%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,52%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>942760</t>
+          <t>945738</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1060315</t>
+          <t>1065572</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,56%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,21%</t>
+          <t>15,28%</t>
         </is>
       </c>
     </row>
@@ -6495,7 +6495,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016</t>
+          <t>Población que consume fruta fresca (excluyendo zumos) al menos 3 veces por semana en 2016 (tasa de respuesta: 99,83%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>272191</t>
+          <t>270795</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>308681</t>
+          <t>309932</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>65,04%</t>
+          <t>64,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>74,06%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>243530</t>
+          <t>241945</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>279802</t>
+          <t>277998</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,29%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,88%</t>
+          <t>70,42%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>526174</t>
+          <t>524309</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>578466</t>
+          <t>577007</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,7%</t>
+          <t>64,47%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>71,13%</t>
+          <t>70,95%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>109795</t>
+          <t>108544</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>146285</t>
+          <t>147681</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>25,94%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>34,96%</t>
+          <t>35,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>114957</t>
+          <t>116761</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>151229</t>
+          <t>152814</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,12%</t>
+          <t>29,58%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,71%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>234769</t>
+          <t>236228</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>287061</t>
+          <t>288926</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>28,87%</t>
+          <t>29,05%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,3%</t>
+          <t>35,53%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>417305</t>
+          <t>416320</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>461416</t>
+          <t>460133</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,79%</t>
+          <t>70,62%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,05%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>402920</t>
+          <t>404787</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>443167</t>
+          <t>442685</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,5%</t>
+          <t>71,83%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,64%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>834893</t>
+          <t>836361</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>892404</t>
+          <t>892300</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,7 +7118,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,41%</t>
+          <t>72,53%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>128097</t>
+          <t>129380</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>172208</t>
+          <t>173193</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,95%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,21%</t>
+          <t>29,38%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120377</t>
+          <t>120859</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>160624</t>
+          <t>158757</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,36%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,5%</t>
+          <t>28,17%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260653</t>
+          <t>260757</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>318164</t>
+          <t>316696</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7236,7 +7236,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,59%</t>
+          <t>27,47%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>491405</t>
+          <t>492176</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>536539</t>
+          <t>537784</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,64%</t>
+          <t>73,76%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,41%</t>
+          <t>80,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>538035</t>
+          <t>538258</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>574358</t>
+          <t>574284</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,55%</t>
+          <t>81,58%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,06%</t>
+          <t>87,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1043389</t>
+          <t>1045833</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1100097</t>
+          <t>1101350</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,63%</t>
+          <t>78,81%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,9%</t>
+          <t>82,99%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>130734</t>
+          <t>129489</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175868</t>
+          <t>175097</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,59%</t>
+          <t>19,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,36%</t>
+          <t>26,24%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85398</t>
+          <t>85472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121721</t>
+          <t>121498</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,94%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,45%</t>
+          <t>18,42%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>226932</t>
+          <t>225679</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>283640</t>
+          <t>281196</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,1%</t>
+          <t>17,01%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,37%</t>
+          <t>21,19%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>494231</t>
+          <t>495647</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>538355</t>
+          <t>538704</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,5%</t>
+          <t>76,72%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,33%</t>
+          <t>83,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>540912</t>
+          <t>538541</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>577257</t>
+          <t>575621</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,48%</t>
+          <t>83,11%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>89,09%</t>
+          <t>88,84%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1048756</t>
+          <t>1048697</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1104184</t>
+          <t>1105100</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,05%</t>
+          <t>81,04%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,33%</t>
+          <t>85,4%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107693</t>
+          <t>107344</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>151817</t>
+          <t>150401</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,67%</t>
+          <t>16,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,5%</t>
+          <t>23,28%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>70708</t>
+          <t>72344</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>107053</t>
+          <t>109424</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>10,91%</t>
+          <t>11,16%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,52%</t>
+          <t>16,89%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>189829</t>
+          <t>188913</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245257</t>
+          <t>245316</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,67%</t>
+          <t>14,6%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,95%</t>
+          <t>18,96%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>393497</t>
+          <t>394167</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>425860</t>
+          <t>425288</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,52%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,3%</t>
+          <t>89,18%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>419944</t>
+          <t>420329</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>452558</t>
+          <t>452941</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,52%</t>
+          <t>84,6%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,09%</t>
+          <t>91,16%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>825502</t>
+          <t>826914</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>869809</t>
+          <t>871239</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,78%</t>
+          <t>84,92%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,48%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51009</t>
+          <t>51581</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>83372</t>
+          <t>82702</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,7%</t>
+          <t>10,82%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,48%</t>
+          <t>17,34%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>44291</t>
+          <t>43908</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76905</t>
+          <t>76520</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,91%</t>
+          <t>8,84%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,48%</t>
+          <t>15,4%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>103909</t>
+          <t>102479</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>148216</t>
+          <t>146804</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,52%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,22%</t>
+          <t>15,08%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>291253</t>
+          <t>292276</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>314093</t>
+          <t>313665</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,47 +8420,47 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
+          <t>87,7%</t>
+        </is>
+      </c>
+      <c r="I19" s="2" t="inlineStr">
+        <is>
+          <t>94,12%</t>
+        </is>
+      </c>
+      <c r="J19" s="2" t="inlineStr">
+        <is>
+          <t>318</t>
+        </is>
+      </c>
+      <c r="K19" s="2" t="inlineStr">
+        <is>
+          <t>340426</t>
+        </is>
+      </c>
+      <c r="L19" s="2" t="inlineStr">
+        <is>
+          <t>328291</t>
+        </is>
+      </c>
+      <c r="M19" s="2" t="inlineStr">
+        <is>
+          <t>351136</t>
+        </is>
+      </c>
+      <c r="N19" s="2" t="inlineStr">
+        <is>
+          <t>90,62%</t>
+        </is>
+      </c>
+      <c r="O19" s="2" t="inlineStr">
+        <is>
           <t>87,39%</t>
         </is>
       </c>
-      <c r="I19" s="2" t="inlineStr">
-        <is>
-          <t>94,25%</t>
-        </is>
-      </c>
-      <c r="J19" s="2" t="inlineStr">
-        <is>
-          <t>318</t>
-        </is>
-      </c>
-      <c r="K19" s="2" t="inlineStr">
-        <is>
-          <t>340426</t>
-        </is>
-      </c>
-      <c r="L19" s="2" t="inlineStr">
-        <is>
-          <t>327974</t>
-        </is>
-      </c>
-      <c r="M19" s="2" t="inlineStr">
-        <is>
-          <t>350775</t>
-        </is>
-      </c>
-      <c r="N19" s="2" t="inlineStr">
-        <is>
-          <t>90,62%</t>
-        </is>
-      </c>
-      <c r="O19" s="2" t="inlineStr">
-        <is>
-          <t>87,3%</t>
-        </is>
-      </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,37%</t>
+          <t>93,47%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>627972</t>
+          <t>625860</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>659359</t>
+          <t>659413</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,7 +8490,7 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,58%</t>
+          <t>88,28%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19178</t>
+          <t>19606</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>42018</t>
+          <t>40995</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,49 +8533,49 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,75%</t>
+          <t>5,88%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
+          <t>12,3%</t>
+        </is>
+      </c>
+      <c r="J20" s="2" t="inlineStr">
+        <is>
+          <t>34</t>
+        </is>
+      </c>
+      <c r="K20" s="2" t="inlineStr">
+        <is>
+          <t>35245</t>
+        </is>
+      </c>
+      <c r="L20" s="2" t="inlineStr">
+        <is>
+          <t>24535</t>
+        </is>
+      </c>
+      <c r="M20" s="2" t="inlineStr">
+        <is>
+          <t>47380</t>
+        </is>
+      </c>
+      <c r="N20" s="2" t="inlineStr">
+        <is>
+          <t>9,38%</t>
+        </is>
+      </c>
+      <c r="O20" s="2" t="inlineStr">
+        <is>
+          <t>6,53%</t>
+        </is>
+      </c>
+      <c r="P20" s="2" t="inlineStr">
+        <is>
           <t>12,61%</t>
         </is>
       </c>
-      <c r="J20" s="2" t="inlineStr">
-        <is>
-          <t>34</t>
-        </is>
-      </c>
-      <c r="K20" s="2" t="inlineStr">
-        <is>
-          <t>35245</t>
-        </is>
-      </c>
-      <c r="L20" s="2" t="inlineStr">
-        <is>
-          <t>24896</t>
-        </is>
-      </c>
-      <c r="M20" s="2" t="inlineStr">
-        <is>
-          <t>47697</t>
-        </is>
-      </c>
-      <c r="N20" s="2" t="inlineStr">
-        <is>
-          <t>9,38%</t>
-        </is>
-      </c>
-      <c r="O20" s="2" t="inlineStr">
-        <is>
-          <t>6,63%</t>
-        </is>
-      </c>
-      <c r="P20" s="2" t="inlineStr">
-        <is>
-          <t>12,7%</t>
-        </is>
-      </c>
       <c r="Q20" s="2" t="inlineStr">
         <is>
           <t>60</t>
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49583</t>
+          <t>49529</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>80970</t>
+          <t>83082</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8608,7 +8608,7 @@
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,42%</t>
+          <t>11,72%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>220895</t>
+          <t>221541</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>238358</t>
+          <t>239025</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,25%</t>
+          <t>86,51%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,07%</t>
+          <t>93,33%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>357990</t>
+          <t>357891</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381735</t>
+          <t>381635</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,44%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,39%</t>
+          <t>95,37%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>584316</t>
+          <t>586217</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>615894</t>
+          <t>616137</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,04%</t>
+          <t>89,33%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,85%</t>
+          <t>93,88%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17742</t>
+          <t>17075</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>35205</t>
+          <t>34559</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,93%</t>
+          <t>6,67%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,75%</t>
+          <t>13,49%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18434</t>
+          <t>18534</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42179</t>
+          <t>42278</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,61%</t>
+          <t>4,63%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,56%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40375</t>
+          <t>40132</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>71953</t>
+          <t>70052</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,15%</t>
+          <t>6,12%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,96%</t>
+          <t>10,67%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2660576</t>
+          <t>2663191</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2752130</t>
+          <t>2759808</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,54%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,24%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2905980</t>
+          <t>2906414</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2993329</t>
+          <t>2999309</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,13%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,76%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5590496</t>
+          <t>5597182</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5724540</t>
+          <t>5726172</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,71%</t>
+          <t>80,81%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,67%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>635420</t>
+          <t>627742</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>726974</t>
+          <t>724359</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,76%</t>
+          <t>18,53%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,46%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>545383</t>
+          <t>539403</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>632732</t>
+          <t>632298</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,24%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,87%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1201723</t>
+          <t>1200091</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1335767</t>
+          <t>1329081</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,33%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,29%</t>
+          <t>19,19%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P36B06_R-Edad-trans_orig.xlsx
+++ b/data/trans_orig/P36B06_R-Edad-trans_orig.xlsx
@@ -732,12 +732,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>301942</t>
+          <t>299080</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>343043</t>
+          <t>342993</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>61,24%</t>
+          <t>60,66%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,57%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -767,12 +767,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>293125</t>
+          <t>290751</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>331978</t>
+          <t>330468</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -782,12 +782,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>62,84%</t>
+          <t>62,34%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>71,17%</t>
+          <t>70,85%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -802,12 +802,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>604272</t>
+          <t>605775</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>662621</t>
+          <t>662260</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -817,12 +817,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>62,98%</t>
+          <t>63,14%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,02%</t>
         </is>
       </c>
     </row>
@@ -845,12 +845,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>149979</t>
+          <t>150029</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>191080</t>
+          <t>193942</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -860,12 +860,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,43%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>38,76%</t>
+          <t>39,34%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -880,12 +880,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>134451</t>
+          <t>135961</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>173304</t>
+          <t>175678</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -895,12 +895,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>28,83%</t>
+          <t>29,15%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>37,16%</t>
+          <t>37,66%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -915,12 +915,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>296830</t>
+          <t>297191</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>355179</t>
+          <t>353676</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -930,12 +930,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,98%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>37,02%</t>
+          <t>36,86%</t>
         </is>
       </c>
     </row>
@@ -1075,12 +1075,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>506754</t>
+          <t>503045</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>554642</t>
+          <t>553530</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1090,12 +1090,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>68,99%</t>
+          <t>68,48%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>75,51%</t>
+          <t>75,36%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1110,12 +1110,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>467360</t>
+          <t>469151</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>507817</t>
+          <t>509798</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1125,12 +1125,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>74,72%</t>
+          <t>75,0%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>81,19%</t>
+          <t>81,5%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1145,12 +1145,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>983873</t>
+          <t>988484</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1050528</t>
+          <t>1051972</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1160,12 +1160,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,34%</t>
+          <t>72,68%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,35%</t>
         </is>
       </c>
     </row>
@@ -1188,12 +1188,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>179899</t>
+          <t>181011</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>227787</t>
+          <t>231496</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1203,12 +1203,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>24,49%</t>
+          <t>24,64%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>31,01%</t>
+          <t>31,52%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1223,12 +1223,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>117677</t>
+          <t>115696</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158134</t>
+          <t>156343</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1238,12 +1238,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>18,81%</t>
+          <t>18,5%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>25,28%</t>
+          <t>25,0%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1258,12 +1258,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>309506</t>
+          <t>308062</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>376161</t>
+          <t>371550</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1273,12 +1273,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,65%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,66%</t>
+          <t>27,32%</t>
         </is>
       </c>
     </row>
@@ -1418,12 +1418,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>471440</t>
+          <t>471057</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>513880</t>
+          <t>513234</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1433,12 +1433,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,92%</t>
+          <t>73,86%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,57%</t>
+          <t>80,47%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1453,12 +1453,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>547388</t>
+          <t>547622</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>587870</t>
+          <t>585944</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1468,12 +1468,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>79,36%</t>
+          <t>79,39%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>85,23%</t>
+          <t>84,95%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1488,12 +1488,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1029371</t>
+          <t>1031415</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1089515</t>
+          <t>1090045</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1503,12 +1503,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>77,69%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,07%</t>
+          <t>82,11%</t>
         </is>
       </c>
     </row>
@@ -1531,12 +1531,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>123906</t>
+          <t>124552</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>166346</t>
+          <t>166729</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1546,12 +1546,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,43%</t>
+          <t>19,53%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,08%</t>
+          <t>26,14%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1566,12 +1566,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>101874</t>
+          <t>103800</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>142356</t>
+          <t>142122</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1581,12 +1581,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>14,77%</t>
+          <t>15,05%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,61%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1601,12 +1601,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>238015</t>
+          <t>237485</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>298159</t>
+          <t>296115</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1616,12 +1616,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,93%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>22,31%</t>
         </is>
       </c>
     </row>
@@ -1761,12 +1761,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>389779</t>
+          <t>389799</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>426312</t>
+          <t>428463</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1781,7 +1781,7 @@
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,53%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1796,12 +1796,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>421925</t>
+          <t>421668</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>454403</t>
+          <t>454464</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1811,12 +1811,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>81,98%</t>
+          <t>81,93%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,29%</t>
+          <t>88,3%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1831,12 +1831,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>825522</t>
+          <t>823129</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>874018</t>
+          <t>874124</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1846,12 +1846,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>79,85%</t>
+          <t>79,62%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>84,54%</t>
+          <t>84,55%</t>
         </is>
       </c>
     </row>
@@ -1874,12 +1874,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>92835</t>
+          <t>90684</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>129368</t>
+          <t>129348</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1889,7 +1889,7 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,47%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
@@ -1909,12 +1909,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>60263</t>
+          <t>60202</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>92741</t>
+          <t>92998</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1924,12 +1924,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,71%</t>
+          <t>11,7%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>18,02%</t>
+          <t>18,07%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1944,12 +1944,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>159795</t>
+          <t>159689</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>208291</t>
+          <t>210684</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1959,12 +1959,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>15,46%</t>
+          <t>15,45%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>20,15%</t>
+          <t>20,38%</t>
         </is>
       </c>
     </row>
@@ -2104,12 +2104,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>298941</t>
+          <t>298962</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>328904</t>
+          <t>328282</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>77,3%</t>
+          <t>77,31%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>85,05%</t>
+          <t>84,89%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2139,12 +2139,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>335054</t>
+          <t>336206</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>363754</t>
+          <t>363256</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -2154,12 +2154,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>82,94%</t>
+          <t>83,22%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,04%</t>
+          <t>89,92%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -2174,12 +2174,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>644059</t>
+          <t>644185</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>685590</t>
+          <t>684962</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -2189,12 +2189,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>81,45%</t>
+          <t>81,47%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,63%</t>
         </is>
       </c>
     </row>
@@ -2217,12 +2217,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>57806</t>
+          <t>58428</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>87769</t>
+          <t>87748</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2232,12 +2232,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,95%</t>
+          <t>15,11%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>22,7%</t>
+          <t>22,69%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -2252,12 +2252,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>40232</t>
+          <t>40730</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>68932</t>
+          <t>67780</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -2267,12 +2267,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,96%</t>
+          <t>10,08%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>17,06%</t>
+          <t>16,78%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -2287,12 +2287,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>105106</t>
+          <t>105734</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146637</t>
+          <t>146511</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -2302,12 +2302,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,37%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>18,55%</t>
+          <t>18,53%</t>
         </is>
       </c>
     </row>
@@ -2447,12 +2447,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>235281</t>
+          <t>234921</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>258863</t>
+          <t>259223</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -2462,12 +2462,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>80,42%</t>
+          <t>80,29%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>88,48%</t>
+          <t>88,6%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -2482,12 +2482,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>292413</t>
+          <t>293774</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>315044</t>
+          <t>316712</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -2497,12 +2497,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>85,27%</t>
+          <t>85,66%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>91,87%</t>
+          <t>92,35%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -2517,12 +2517,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>535068</t>
+          <t>536793</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>569473</t>
+          <t>568936</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -2532,12 +2532,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>84,19%</t>
+          <t>84,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>89,61%</t>
+          <t>89,52%</t>
         </is>
       </c>
     </row>
@@ -2560,12 +2560,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>33720</t>
+          <t>33360</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>57302</t>
+          <t>57662</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2575,12 +2575,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>11,52%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>19,58%</t>
+          <t>19,71%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -2595,12 +2595,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>27890</t>
+          <t>26222</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>50521</t>
+          <t>49160</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -2610,12 +2610,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>8,13%</t>
+          <t>7,65%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>14,73%</t>
+          <t>14,34%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -2630,12 +2630,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>66044</t>
+          <t>66581</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>100449</t>
+          <t>98724</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -2645,12 +2645,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>10,39%</t>
+          <t>10,48%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>15,81%</t>
+          <t>15,53%</t>
         </is>
       </c>
     </row>
@@ -2790,12 +2790,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>165516</t>
+          <t>165963</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>187327</t>
+          <t>186614</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -2805,12 +2805,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>79,07%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>89,25%</t>
+          <t>88,91%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -2825,12 +2825,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>276406</t>
+          <t>276143</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>301469</t>
+          <t>302448</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -2840,12 +2840,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,7%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>90,29%</t>
+          <t>90,58%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -2860,12 +2860,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>449438</t>
+          <t>449475</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>483048</t>
+          <t>481813</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -2875,12 +2875,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>82,65%</t>
+          <t>82,66%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>88,83%</t>
+          <t>88,6%</t>
         </is>
       </c>
     </row>
@@ -2903,12 +2903,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>22556</t>
+          <t>23269</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>44367</t>
+          <t>43920</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -2918,12 +2918,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>10,75%</t>
+          <t>11,09%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -2938,12 +2938,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>32439</t>
+          <t>31460</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>57502</t>
+          <t>57765</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -2953,12 +2953,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>9,71%</t>
+          <t>9,42%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,3%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -2973,12 +2973,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>60743</t>
+          <t>61978</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>94353</t>
+          <t>94316</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -2988,12 +2988,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>11,17%</t>
+          <t>11,4%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>17,35%</t>
+          <t>17,34%</t>
         </is>
       </c>
     </row>
@@ -3133,12 +3133,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2451498</t>
+          <t>2446669</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2550722</t>
+          <t>2543041</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -3148,12 +3148,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>74,89%</t>
+          <t>74,74%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>77,92%</t>
+          <t>77,68%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -3168,12 +3168,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2713392</t>
+          <t>2712791</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2798214</t>
+          <t>2798060</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -3183,12 +3183,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>80,35%</t>
+          <t>80,33%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>82,86%</t>
+          <t>82,85%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -3203,12 +3203,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5185270</t>
+          <t>5188156</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5322071</t>
+          <t>5314879</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -3218,12 +3218,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>77,96%</t>
+          <t>78,01%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>80,02%</t>
+          <t>79,91%</t>
         </is>
       </c>
     </row>
@@ -3246,12 +3246,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>722949</t>
+          <t>730630</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>822173</t>
+          <t>827002</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -3261,12 +3261,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>22,08%</t>
+          <t>22,32%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>25,11%</t>
+          <t>25,26%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -3281,12 +3281,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>578948</t>
+          <t>579102</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>663770</t>
+          <t>664371</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -3296,12 +3296,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>17,14%</t>
+          <t>17,15%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>19,65%</t>
+          <t>19,67%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -3316,12 +3316,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1328762</t>
+          <t>1335954</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1465563</t>
+          <t>1462677</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -3331,12 +3331,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>19,98%</t>
+          <t>20,09%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>22,04%</t>
+          <t>21,99%</t>
         </is>
       </c>
     </row>
@@ -3711,12 +3711,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>312955</t>
+          <t>312043</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>351381</t>
+          <t>348610</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3726,12 +3726,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>68,91%</t>
+          <t>68,71%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>77,37%</t>
+          <t>76,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3746,12 +3746,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>313549</t>
+          <t>313117</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>348436</t>
+          <t>347598</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3761,12 +3761,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>72,88%</t>
+          <t>72,78%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,79%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -3781,12 +3781,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>636471</t>
+          <t>636013</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>689055</t>
+          <t>688255</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -3796,12 +3796,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>71,97%</t>
+          <t>71,92%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>77,91%</t>
+          <t>77,82%</t>
         </is>
       </c>
     </row>
@@ -3824,12 +3824,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>102765</t>
+          <t>105536</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>141191</t>
+          <t>142103</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -3839,12 +3839,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>22,63%</t>
+          <t>23,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>31,09%</t>
+          <t>31,29%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -3859,12 +3859,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>81794</t>
+          <t>82632</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>116681</t>
+          <t>117113</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -3874,12 +3874,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,21%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>27,12%</t>
+          <t>27,22%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -3894,12 +3894,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>195321</t>
+          <t>196121</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>247905</t>
+          <t>248363</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -3909,12 +3909,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>22,09%</t>
+          <t>22,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>28,03%</t>
+          <t>28,08%</t>
         </is>
       </c>
     </row>
@@ -4054,12 +4054,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>501516</t>
+          <t>499702</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>546181</t>
+          <t>545453</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4069,12 +4069,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>73,09%</t>
+          <t>72,83%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>79,6%</t>
+          <t>79,5%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4089,12 +4089,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>498469</t>
+          <t>497594</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>534702</t>
+          <t>533508</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4104,12 +4104,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>81,81%</t>
+          <t>81,67%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>87,76%</t>
+          <t>87,57%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4124,12 +4124,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>1011924</t>
+          <t>1007895</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>1069443</t>
+          <t>1068677</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4139,12 +4139,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>78,12%</t>
+          <t>77,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>82,56%</t>
+          <t>82,5%</t>
         </is>
       </c>
     </row>
@@ -4167,12 +4167,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>139947</t>
+          <t>140675</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>184612</t>
+          <t>186426</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4182,12 +4182,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>20,4%</t>
+          <t>20,5%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>26,91%</t>
+          <t>27,17%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4202,12 +4202,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>74567</t>
+          <t>75761</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>110800</t>
+          <t>111675</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4217,12 +4217,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>12,24%</t>
+          <t>12,43%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>18,19%</t>
+          <t>18,33%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4237,12 +4237,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>225955</t>
+          <t>226721</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>283474</t>
+          <t>287503</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4252,12 +4252,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>17,44%</t>
+          <t>17,5%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>21,88%</t>
+          <t>22,19%</t>
         </is>
       </c>
     </row>
@@ -4397,12 +4397,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>541813</t>
+          <t>542991</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>580555</t>
+          <t>584250</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4412,12 +4412,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,63%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>85,14%</t>
+          <t>85,68%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4432,12 +4432,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>600332</t>
+          <t>597368</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>634855</t>
+          <t>636592</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4447,12 +4447,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>84,59%</t>
+          <t>84,18%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>89,46%</t>
+          <t>89,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4467,12 +4467,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1150923</t>
+          <t>1151515</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1205305</t>
+          <t>1205797</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4482,12 +4482,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>82,71%</t>
+          <t>82,75%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>86,62%</t>
+          <t>86,65%</t>
         </is>
       </c>
     </row>
@@ -4510,12 +4510,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>101308</t>
+          <t>97613</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>140050</t>
+          <t>138872</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4525,12 +4525,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>14,86%</t>
+          <t>14,32%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,37%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4545,12 +4545,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>74817</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109340</t>
+          <t>112304</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4560,12 +4560,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>10,54%</t>
+          <t>10,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>15,41%</t>
+          <t>15,82%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4580,12 +4580,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>186229</t>
+          <t>185737</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>240611</t>
+          <t>240019</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4595,12 +4595,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>13,38%</t>
+          <t>13,35%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>17,29%</t>
+          <t>17,25%</t>
         </is>
       </c>
     </row>
@@ -4740,12 +4740,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>513360</t>
+          <t>514075</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>547537</t>
+          <t>548215</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4755,12 +4755,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>83,81%</t>
+          <t>83,92%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>89,38%</t>
+          <t>89,5%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -4775,12 +4775,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>540760</t>
+          <t>540189</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>571607</t>
+          <t>571984</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -4790,12 +4790,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>87,91%</t>
+          <t>87,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>92,92%</t>
+          <t>92,98%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -4810,12 +4810,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1064517</t>
+          <t>1062891</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1112607</t>
+          <t>1113227</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -4825,12 +4825,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>86,71%</t>
+          <t>86,58%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>90,63%</t>
+          <t>90,68%</t>
         </is>
       </c>
     </row>
@@ -4853,12 +4853,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>65027</t>
+          <t>64349</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>99204</t>
+          <t>98489</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -4868,12 +4868,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>10,62%</t>
+          <t>10,5%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>16,19%</t>
+          <t>16,08%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -4888,12 +4888,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>43531</t>
+          <t>43154</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>74378</t>
+          <t>74949</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -4903,12 +4903,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>7,08%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>12,09%</t>
+          <t>12,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -4923,12 +4923,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>115096</t>
+          <t>114476</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>163186</t>
+          <t>164812</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -4938,12 +4938,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>9,37%</t>
+          <t>9,32%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>13,29%</t>
+          <t>13,42%</t>
         </is>
       </c>
     </row>
@@ -5083,12 +5083,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>371344</t>
+          <t>371333</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>397513</t>
+          <t>397354</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -5103,7 +5103,7 @@
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>92,57%</t>
+          <t>92,53%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -5118,12 +5118,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>376266</t>
+          <t>378717</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>406298</t>
+          <t>407794</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -5133,12 +5133,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>84,57%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>90,73%</t>
+          <t>91,07%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -5153,12 +5153,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>756984</t>
+          <t>754748</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>795800</t>
+          <t>796017</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -5168,12 +5168,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>86,29%</t>
+          <t>86,04%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>90,72%</t>
+          <t>90,74%</t>
         </is>
       </c>
     </row>
@@ -5196,12 +5196,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>31916</t>
+          <t>32075</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>58085</t>
+          <t>58096</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -5211,7 +5211,7 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>7,43%</t>
+          <t>7,47%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
@@ -5231,12 +5231,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>41502</t>
+          <t>40006</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>71534</t>
+          <t>69083</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -5246,12 +5246,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>9,27%</t>
+          <t>8,93%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>15,43%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -5266,12 +5266,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>81429</t>
+          <t>81212</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>120245</t>
+          <t>122481</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -5281,12 +5281,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>9,28%</t>
+          <t>9,26%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>13,71%</t>
+          <t>13,96%</t>
         </is>
       </c>
     </row>
@@ -5426,12 +5426,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>269312</t>
+          <t>269638</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>290350</t>
+          <t>290960</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -5441,12 +5441,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,21%</t>
+          <t>87,32%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,02%</t>
+          <t>94,22%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -5461,12 +5461,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>323536</t>
+          <t>322473</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>341152</t>
+          <t>340708</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -5476,12 +5476,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>91,4%</t>
+          <t>91,1%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>96,37%</t>
+          <t>96,25%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -5496,12 +5496,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>600255</t>
+          <t>599623</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>627121</t>
+          <t>626540</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>90,56%</t>
+          <t>90,47%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>94,62%</t>
+          <t>94,53%</t>
         </is>
       </c>
     </row>
@@ -5539,12 +5539,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>18454</t>
+          <t>17844</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>39492</t>
+          <t>39166</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -5554,12 +5554,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,98%</t>
+          <t>5,78%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,79%</t>
+          <t>12,68%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -5574,12 +5574,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>12844</t>
+          <t>13288</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>30460</t>
+          <t>31523</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -5589,12 +5589,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>3,63%</t>
+          <t>3,75%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>8,6%</t>
+          <t>8,9%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -5609,12 +5609,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>35679</t>
+          <t>36260</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>62545</t>
+          <t>63177</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -5624,12 +5624,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>5,38%</t>
+          <t>5,47%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>9,44%</t>
+          <t>9,53%</t>
         </is>
       </c>
     </row>
@@ -5769,12 +5769,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>227632</t>
+          <t>228269</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>243268</t>
+          <t>243434</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -5784,12 +5784,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>91,5%</t>
+          <t>91,75%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>97,78%</t>
+          <t>97,85%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -5804,12 +5804,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>353797</t>
+          <t>354718</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>372770</t>
+          <t>372440</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -5819,12 +5819,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>91,93%</t>
+          <t>92,17%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>96,86%</t>
+          <t>96,77%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -5839,12 +5839,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>589359</t>
+          <t>587630</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>612722</t>
+          <t>612624</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -5854,12 +5854,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,74%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>96,7%</t>
+          <t>96,68%</t>
         </is>
       </c>
     </row>
@@ -5882,12 +5882,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>5514</t>
+          <t>5348</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>21150</t>
+          <t>20513</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -5897,12 +5897,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>2,22%</t>
+          <t>2,15%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>8,5%</t>
+          <t>8,25%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -5917,12 +5917,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>12097</t>
+          <t>12427</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>31070</t>
+          <t>30149</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -5932,12 +5932,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>3,14%</t>
+          <t>3,23%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>8,07%</t>
+          <t>7,83%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -5952,12 +5952,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>20927</t>
+          <t>21025</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>44290</t>
+          <t>46019</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -5967,12 +5967,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>3,3%</t>
+          <t>3,32%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,26%</t>
         </is>
       </c>
     </row>
@@ -6112,12 +6112,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2801621</t>
+          <t>2807106</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2893006</t>
+          <t>2901259</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -6127,12 +6127,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>81,88%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>84,55%</t>
+          <t>84,79%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -6147,12 +6147,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>3070752</t>
+          <t>3078052</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>3152914</t>
+          <t>3157898</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -6162,12 +6162,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>86,48%</t>
+          <t>86,68%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>88,79%</t>
+          <t>88,93%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -6182,12 +6182,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5907117</t>
+          <t>5907769</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>6026951</t>
+          <t>6028474</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -6197,12 +6197,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>84,72%</t>
+          <t>84,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>86,44%</t>
+          <t>86,46%</t>
         </is>
       </c>
     </row>
@@ -6225,12 +6225,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>528711</t>
+          <t>520458</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>620096</t>
+          <t>614611</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -6240,12 +6240,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>15,45%</t>
+          <t>15,21%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>18,12%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -6260,12 +6260,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>398058</t>
+          <t>393074</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>480220</t>
+          <t>472920</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -6275,12 +6275,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>11,21%</t>
+          <t>11,07%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>13,52%</t>
+          <t>13,32%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -6295,12 +6295,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>945738</t>
+          <t>944215</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1065572</t>
+          <t>1064920</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -6310,12 +6310,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>13,56%</t>
+          <t>13,54%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>15,28%</t>
+          <t>15,27%</t>
         </is>
       </c>
     </row>
@@ -6690,12 +6690,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>270795</t>
+          <t>271767</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>309932</t>
+          <t>309342</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -6705,12 +6705,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>64,71%</t>
+          <t>64,94%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>74,06%</t>
+          <t>73,92%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -6725,12 +6725,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>241945</t>
+          <t>243246</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>277998</t>
+          <t>279018</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -6740,12 +6740,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>61,29%</t>
+          <t>61,62%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>70,42%</t>
+          <t>70,68%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -6760,12 +6760,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>524309</t>
+          <t>526328</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>577007</t>
+          <t>578787</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -6775,12 +6775,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>64,47%</t>
+          <t>64,72%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>70,95%</t>
+          <t>71,17%</t>
         </is>
       </c>
     </row>
@@ -6803,12 +6803,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>108544</t>
+          <t>109134</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>147681</t>
+          <t>146709</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -6818,12 +6818,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>25,94%</t>
+          <t>26,08%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>35,29%</t>
+          <t>35,06%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -6838,12 +6838,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>116761</t>
+          <t>115741</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>152814</t>
+          <t>151513</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -6853,12 +6853,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>29,58%</t>
+          <t>29,32%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>38,71%</t>
+          <t>38,38%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -6873,12 +6873,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>236228</t>
+          <t>234448</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>288926</t>
+          <t>286907</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -6888,12 +6888,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>29,05%</t>
+          <t>28,83%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>35,53%</t>
+          <t>35,28%</t>
         </is>
       </c>
     </row>
@@ -7033,12 +7033,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>416320</t>
+          <t>418960</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>460133</t>
+          <t>460480</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -7048,12 +7048,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>70,62%</t>
+          <t>71,07%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>78,05%</t>
+          <t>78,11%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -7068,12 +7068,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>404787</t>
+          <t>403052</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>442685</t>
+          <t>444233</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -7083,12 +7083,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>71,83%</t>
+          <t>71,52%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,83%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -7103,12 +7103,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>836361</t>
+          <t>830468</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>892300</t>
+          <t>891314</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -7118,12 +7118,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>72,53%</t>
+          <t>72,02%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>77,39%</t>
+          <t>77,3%</t>
         </is>
       </c>
     </row>
@@ -7146,12 +7146,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>129380</t>
+          <t>129033</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>173193</t>
+          <t>170553</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -7161,12 +7161,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>21,95%</t>
+          <t>21,89%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>29,38%</t>
+          <t>28,93%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -7181,12 +7181,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>120859</t>
+          <t>119311</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>158757</t>
+          <t>160492</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -7196,12 +7196,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,17%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>28,17%</t>
+          <t>28,48%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -7216,12 +7216,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>260757</t>
+          <t>261743</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>316696</t>
+          <t>322589</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -7231,12 +7231,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>22,61%</t>
+          <t>22,7%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>27,47%</t>
+          <t>27,98%</t>
         </is>
       </c>
     </row>
@@ -7376,12 +7376,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>492176</t>
+          <t>492232</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>537784</t>
+          <t>536613</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -7391,12 +7391,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>73,76%</t>
+          <t>73,77%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>80,59%</t>
+          <t>80,42%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -7411,12 +7411,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>538258</t>
+          <t>535954</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>574284</t>
+          <t>573608</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -7426,12 +7426,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>81,58%</t>
+          <t>81,24%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>87,04%</t>
+          <t>86,94%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -7446,12 +7446,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>1045833</t>
+          <t>1043726</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>1101350</t>
+          <t>1102663</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -7461,12 +7461,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>78,81%</t>
+          <t>78,65%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,09%</t>
         </is>
       </c>
     </row>
@@ -7489,12 +7489,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>129489</t>
+          <t>130660</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>175097</t>
+          <t>175041</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -7504,12 +7504,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>19,41%</t>
+          <t>19,58%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>26,24%</t>
+          <t>26,23%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -7524,12 +7524,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>85472</t>
+          <t>86148</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>121498</t>
+          <t>123802</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -7539,12 +7539,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>12,96%</t>
+          <t>13,06%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>18,42%</t>
+          <t>18,76%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -7559,12 +7559,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>225679</t>
+          <t>224366</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>281196</t>
+          <t>283303</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -7574,12 +7574,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,91%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>21,19%</t>
+          <t>21,35%</t>
         </is>
       </c>
     </row>
@@ -7719,12 +7719,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>495647</t>
+          <t>494755</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>538704</t>
+          <t>537205</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -7734,12 +7734,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>76,72%</t>
+          <t>76,58%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>83,38%</t>
+          <t>83,15%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -7754,12 +7754,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>538541</t>
+          <t>541267</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>575621</t>
+          <t>577001</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -7769,12 +7769,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>83,11%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>88,84%</t>
+          <t>89,05%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -7789,12 +7789,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>1048697</t>
+          <t>1045842</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>1105100</t>
+          <t>1104379</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -7804,12 +7804,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>81,04%</t>
+          <t>80,82%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>85,4%</t>
+          <t>85,35%</t>
         </is>
       </c>
     </row>
@@ -7832,12 +7832,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>107344</t>
+          <t>108843</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>150401</t>
+          <t>151293</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -7847,12 +7847,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>16,62%</t>
+          <t>16,85%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>23,28%</t>
+          <t>23,42%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -7867,12 +7867,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>72344</t>
+          <t>70964</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>109424</t>
+          <t>106698</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -7882,12 +7882,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>11,16%</t>
+          <t>10,95%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>16,89%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -7902,12 +7902,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>188913</t>
+          <t>189634</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>245316</t>
+          <t>248171</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -7917,12 +7917,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>14,6%</t>
+          <t>14,65%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>18,96%</t>
+          <t>19,18%</t>
         </is>
       </c>
     </row>
@@ -8062,12 +8062,12 @@
       </c>
       <c r="E16" s="2" t="inlineStr">
         <is>
-          <t>394167</t>
+          <t>393586</t>
         </is>
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>425288</t>
+          <t>424593</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -8077,12 +8077,12 @@
       </c>
       <c r="H16" s="2" t="inlineStr">
         <is>
-          <t>82,66%</t>
+          <t>82,54%</t>
         </is>
       </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>89,18%</t>
+          <t>89,04%</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -8097,12 +8097,12 @@
       </c>
       <c r="L16" s="2" t="inlineStr">
         <is>
-          <t>420329</t>
+          <t>420870</t>
         </is>
       </c>
       <c r="M16" s="2" t="inlineStr">
         <is>
-          <t>452941</t>
+          <t>451515</t>
         </is>
       </c>
       <c r="N16" s="2" t="inlineStr">
@@ -8112,12 +8112,12 @@
       </c>
       <c r="O16" s="2" t="inlineStr">
         <is>
-          <t>84,6%</t>
+          <t>84,71%</t>
         </is>
       </c>
       <c r="P16" s="2" t="inlineStr">
         <is>
-          <t>91,16%</t>
+          <t>90,88%</t>
         </is>
       </c>
       <c r="Q16" s="2" t="inlineStr">
@@ -8132,12 +8132,12 @@
       </c>
       <c r="S16" s="2" t="inlineStr">
         <is>
-          <t>826914</t>
+          <t>825399</t>
         </is>
       </c>
       <c r="T16" s="2" t="inlineStr">
         <is>
-          <t>871239</t>
+          <t>869037</t>
         </is>
       </c>
       <c r="U16" s="2" t="inlineStr">
@@ -8147,12 +8147,12 @@
       </c>
       <c r="V16" s="2" t="inlineStr">
         <is>
-          <t>84,92%</t>
+          <t>84,77%</t>
         </is>
       </c>
       <c r="W16" s="2" t="inlineStr">
         <is>
-          <t>89,48%</t>
+          <t>89,25%</t>
         </is>
       </c>
     </row>
@@ -8175,12 +8175,12 @@
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>51581</t>
+          <t>52276</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>82702</t>
+          <t>83283</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -8190,12 +8190,12 @@
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>10,82%</t>
+          <t>10,96%</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>17,34%</t>
+          <t>17,46%</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
@@ -8210,12 +8210,12 @@
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>43908</t>
+          <t>45334</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>76520</t>
+          <t>75979</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
@@ -8225,12 +8225,12 @@
       </c>
       <c r="O17" s="2" t="inlineStr">
         <is>
-          <t>8,84%</t>
+          <t>9,12%</t>
         </is>
       </c>
       <c r="P17" s="2" t="inlineStr">
         <is>
-          <t>15,4%</t>
+          <t>15,29%</t>
         </is>
       </c>
       <c r="Q17" s="2" t="inlineStr">
@@ -8245,12 +8245,12 @@
       </c>
       <c r="S17" s="2" t="inlineStr">
         <is>
-          <t>102479</t>
+          <t>104681</t>
         </is>
       </c>
       <c r="T17" s="2" t="inlineStr">
         <is>
-          <t>146804</t>
+          <t>148319</t>
         </is>
       </c>
       <c r="U17" s="2" t="inlineStr">
@@ -8260,12 +8260,12 @@
       </c>
       <c r="V17" s="2" t="inlineStr">
         <is>
-          <t>10,52%</t>
+          <t>10,75%</t>
         </is>
       </c>
       <c r="W17" s="2" t="inlineStr">
         <is>
-          <t>15,08%</t>
+          <t>15,23%</t>
         </is>
       </c>
     </row>
@@ -8405,12 +8405,12 @@
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>292276</t>
+          <t>292217</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>313665</t>
+          <t>313920</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
@@ -8420,12 +8420,12 @@
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,68%</t>
         </is>
       </c>
       <c r="I19" s="2" t="inlineStr">
         <is>
-          <t>94,12%</t>
+          <t>94,19%</t>
         </is>
       </c>
       <c r="J19" s="2" t="inlineStr">
@@ -8440,12 +8440,12 @@
       </c>
       <c r="L19" s="2" t="inlineStr">
         <is>
-          <t>328291</t>
+          <t>327960</t>
         </is>
       </c>
       <c r="M19" s="2" t="inlineStr">
         <is>
-          <t>351136</t>
+          <t>350655</t>
         </is>
       </c>
       <c r="N19" s="2" t="inlineStr">
@@ -8455,12 +8455,12 @@
       </c>
       <c r="O19" s="2" t="inlineStr">
         <is>
-          <t>87,39%</t>
+          <t>87,3%</t>
         </is>
       </c>
       <c r="P19" s="2" t="inlineStr">
         <is>
-          <t>93,47%</t>
+          <t>93,34%</t>
         </is>
       </c>
       <c r="Q19" s="2" t="inlineStr">
@@ -8475,12 +8475,12 @@
       </c>
       <c r="S19" s="2" t="inlineStr">
         <is>
-          <t>625860</t>
+          <t>628996</t>
         </is>
       </c>
       <c r="T19" s="2" t="inlineStr">
         <is>
-          <t>659413</t>
+          <t>659153</t>
         </is>
       </c>
       <c r="U19" s="2" t="inlineStr">
@@ -8490,12 +8490,12 @@
       </c>
       <c r="V19" s="2" t="inlineStr">
         <is>
-          <t>88,28%</t>
+          <t>88,72%</t>
         </is>
       </c>
       <c r="W19" s="2" t="inlineStr">
         <is>
-          <t>93,01%</t>
+          <t>92,98%</t>
         </is>
       </c>
     </row>
@@ -8518,12 +8518,12 @@
       </c>
       <c r="E20" s="2" t="inlineStr">
         <is>
-          <t>19606</t>
+          <t>19351</t>
         </is>
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>40995</t>
+          <t>41054</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -8533,12 +8533,12 @@
       </c>
       <c r="H20" s="2" t="inlineStr">
         <is>
-          <t>5,88%</t>
+          <t>5,81%</t>
         </is>
       </c>
       <c r="I20" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,32%</t>
         </is>
       </c>
       <c r="J20" s="2" t="inlineStr">
@@ -8553,12 +8553,12 @@
       </c>
       <c r="L20" s="2" t="inlineStr">
         <is>
-          <t>24535</t>
+          <t>25016</t>
         </is>
       </c>
       <c r="M20" s="2" t="inlineStr">
         <is>
-          <t>47380</t>
+          <t>47711</t>
         </is>
       </c>
       <c r="N20" s="2" t="inlineStr">
@@ -8568,12 +8568,12 @@
       </c>
       <c r="O20" s="2" t="inlineStr">
         <is>
-          <t>6,53%</t>
+          <t>6,66%</t>
         </is>
       </c>
       <c r="P20" s="2" t="inlineStr">
         <is>
-          <t>12,61%</t>
+          <t>12,7%</t>
         </is>
       </c>
       <c r="Q20" s="2" t="inlineStr">
@@ -8588,12 +8588,12 @@
       </c>
       <c r="S20" s="2" t="inlineStr">
         <is>
-          <t>49529</t>
+          <t>49789</t>
         </is>
       </c>
       <c r="T20" s="2" t="inlineStr">
         <is>
-          <t>83082</t>
+          <t>79946</t>
         </is>
       </c>
       <c r="U20" s="2" t="inlineStr">
@@ -8603,12 +8603,12 @@
       </c>
       <c r="V20" s="2" t="inlineStr">
         <is>
-          <t>6,99%</t>
+          <t>7,02%</t>
         </is>
       </c>
       <c r="W20" s="2" t="inlineStr">
         <is>
-          <t>11,72%</t>
+          <t>11,28%</t>
         </is>
       </c>
     </row>
@@ -8748,12 +8748,12 @@
       </c>
       <c r="E22" s="2" t="inlineStr">
         <is>
-          <t>221541</t>
+          <t>221100</t>
         </is>
       </c>
       <c r="F22" s="2" t="inlineStr">
         <is>
-          <t>239025</t>
+          <t>239113</t>
         </is>
       </c>
       <c r="G22" s="2" t="inlineStr">
@@ -8763,12 +8763,12 @@
       </c>
       <c r="H22" s="2" t="inlineStr">
         <is>
-          <t>86,51%</t>
+          <t>86,33%</t>
         </is>
       </c>
       <c r="I22" s="2" t="inlineStr">
         <is>
-          <t>93,33%</t>
+          <t>93,37%</t>
         </is>
       </c>
       <c r="J22" s="2" t="inlineStr">
@@ -8783,12 +8783,12 @@
       </c>
       <c r="L22" s="2" t="inlineStr">
         <is>
-          <t>357891</t>
+          <t>357281</t>
         </is>
       </c>
       <c r="M22" s="2" t="inlineStr">
         <is>
-          <t>381635</t>
+          <t>380835</t>
         </is>
       </c>
       <c r="N22" s="2" t="inlineStr">
@@ -8798,12 +8798,12 @@
       </c>
       <c r="O22" s="2" t="inlineStr">
         <is>
-          <t>89,44%</t>
+          <t>89,28%</t>
         </is>
       </c>
       <c r="P22" s="2" t="inlineStr">
         <is>
-          <t>95,37%</t>
+          <t>95,17%</t>
         </is>
       </c>
       <c r="Q22" s="2" t="inlineStr">
@@ -8818,12 +8818,12 @@
       </c>
       <c r="S22" s="2" t="inlineStr">
         <is>
-          <t>586217</t>
+          <t>586476</t>
         </is>
       </c>
       <c r="T22" s="2" t="inlineStr">
         <is>
-          <t>616137</t>
+          <t>615326</t>
         </is>
       </c>
       <c r="U22" s="2" t="inlineStr">
@@ -8833,12 +8833,12 @@
       </c>
       <c r="V22" s="2" t="inlineStr">
         <is>
-          <t>89,33%</t>
+          <t>89,37%</t>
         </is>
       </c>
       <c r="W22" s="2" t="inlineStr">
         <is>
-          <t>93,88%</t>
+          <t>93,76%</t>
         </is>
       </c>
     </row>
@@ -8861,12 +8861,12 @@
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>17075</t>
+          <t>16987</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>34559</t>
+          <t>35000</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -8876,12 +8876,12 @@
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>6,67%</t>
+          <t>6,63%</t>
         </is>
       </c>
       <c r="I23" s="2" t="inlineStr">
         <is>
-          <t>13,49%</t>
+          <t>13,67%</t>
         </is>
       </c>
       <c r="J23" s="2" t="inlineStr">
@@ -8896,12 +8896,12 @@
       </c>
       <c r="L23" s="2" t="inlineStr">
         <is>
-          <t>18534</t>
+          <t>19334</t>
         </is>
       </c>
       <c r="M23" s="2" t="inlineStr">
         <is>
-          <t>42278</t>
+          <t>42888</t>
         </is>
       </c>
       <c r="N23" s="2" t="inlineStr">
@@ -8911,12 +8911,12 @@
       </c>
       <c r="O23" s="2" t="inlineStr">
         <is>
-          <t>4,63%</t>
+          <t>4,83%</t>
         </is>
       </c>
       <c r="P23" s="2" t="inlineStr">
         <is>
-          <t>10,56%</t>
+          <t>10,72%</t>
         </is>
       </c>
       <c r="Q23" s="2" t="inlineStr">
@@ -8931,12 +8931,12 @@
       </c>
       <c r="S23" s="2" t="inlineStr">
         <is>
-          <t>40132</t>
+          <t>40943</t>
         </is>
       </c>
       <c r="T23" s="2" t="inlineStr">
         <is>
-          <t>70052</t>
+          <t>69793</t>
         </is>
       </c>
       <c r="U23" s="2" t="inlineStr">
@@ -8946,12 +8946,12 @@
       </c>
       <c r="V23" s="2" t="inlineStr">
         <is>
-          <t>6,12%</t>
+          <t>6,24%</t>
         </is>
       </c>
       <c r="W23" s="2" t="inlineStr">
         <is>
-          <t>10,67%</t>
+          <t>10,63%</t>
         </is>
       </c>
     </row>
@@ -9091,12 +9091,12 @@
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>2663191</t>
+          <t>2663723</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>2759808</t>
+          <t>2756120</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
@@ -9106,12 +9106,12 @@
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>78,62%</t>
+          <t>78,63%</t>
         </is>
       </c>
       <c r="I25" s="2" t="inlineStr">
         <is>
-          <t>81,47%</t>
+          <t>81,36%</t>
         </is>
       </c>
       <c r="J25" s="2" t="inlineStr">
@@ -9126,12 +9126,12 @@
       </c>
       <c r="L25" s="2" t="inlineStr">
         <is>
-          <t>2906414</t>
+          <t>2902820</t>
         </is>
       </c>
       <c r="M25" s="2" t="inlineStr">
         <is>
-          <t>2999309</t>
+          <t>2994356</t>
         </is>
       </c>
       <c r="N25" s="2" t="inlineStr">
@@ -9141,12 +9141,12 @@
       </c>
       <c r="O25" s="2" t="inlineStr">
         <is>
-          <t>82,13%</t>
+          <t>82,03%</t>
         </is>
       </c>
       <c r="P25" s="2" t="inlineStr">
         <is>
-          <t>84,76%</t>
+          <t>84,62%</t>
         </is>
       </c>
       <c r="Q25" s="2" t="inlineStr">
@@ -9161,12 +9161,12 @@
       </c>
       <c r="S25" s="2" t="inlineStr">
         <is>
-          <t>5597182</t>
+          <t>5591746</t>
         </is>
       </c>
       <c r="T25" s="2" t="inlineStr">
         <is>
-          <t>5726172</t>
+          <t>5728970</t>
         </is>
       </c>
       <c r="U25" s="2" t="inlineStr">
@@ -9176,12 +9176,12 @@
       </c>
       <c r="V25" s="2" t="inlineStr">
         <is>
-          <t>80,81%</t>
+          <t>80,73%</t>
         </is>
       </c>
       <c r="W25" s="2" t="inlineStr">
         <is>
-          <t>82,67%</t>
+          <t>82,71%</t>
         </is>
       </c>
     </row>
@@ -9204,12 +9204,12 @@
       </c>
       <c r="E26" s="2" t="inlineStr">
         <is>
-          <t>627742</t>
+          <t>631430</t>
         </is>
       </c>
       <c r="F26" s="2" t="inlineStr">
         <is>
-          <t>724359</t>
+          <t>723827</t>
         </is>
       </c>
       <c r="G26" s="2" t="inlineStr">
@@ -9219,12 +9219,12 @@
       </c>
       <c r="H26" s="2" t="inlineStr">
         <is>
-          <t>18,53%</t>
+          <t>18,64%</t>
         </is>
       </c>
       <c r="I26" s="2" t="inlineStr">
         <is>
-          <t>21,38%</t>
+          <t>21,37%</t>
         </is>
       </c>
       <c r="J26" s="2" t="inlineStr">
@@ -9239,12 +9239,12 @@
       </c>
       <c r="L26" s="2" t="inlineStr">
         <is>
-          <t>539403</t>
+          <t>544356</t>
         </is>
       </c>
       <c r="M26" s="2" t="inlineStr">
         <is>
-          <t>632298</t>
+          <t>635892</t>
         </is>
       </c>
       <c r="N26" s="2" t="inlineStr">
@@ -9254,12 +9254,12 @@
       </c>
       <c r="O26" s="2" t="inlineStr">
         <is>
-          <t>15,24%</t>
+          <t>15,38%</t>
         </is>
       </c>
       <c r="P26" s="2" t="inlineStr">
         <is>
-          <t>17,87%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="Q26" s="2" t="inlineStr">
@@ -9274,12 +9274,12 @@
       </c>
       <c r="S26" s="2" t="inlineStr">
         <is>
-          <t>1200091</t>
+          <t>1197293</t>
         </is>
       </c>
       <c r="T26" s="2" t="inlineStr">
         <is>
-          <t>1329081</t>
+          <t>1334517</t>
         </is>
       </c>
       <c r="U26" s="2" t="inlineStr">
@@ -9289,12 +9289,12 @@
       </c>
       <c r="V26" s="2" t="inlineStr">
         <is>
-          <t>17,33%</t>
+          <t>17,29%</t>
         </is>
       </c>
       <c r="W26" s="2" t="inlineStr">
         <is>
-          <t>19,19%</t>
+          <t>19,27%</t>
         </is>
       </c>
     </row>
